--- a/research/traditional_assets/database/data/south_korea/south_korea_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_hospitals_healthcare_facilities.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.105</v>
+        <v>0.15</v>
       </c>
       <c r="G2">
-        <v>0.04968944099378882</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="H2">
-        <v>0.03072016115494376</v>
+        <v>0.05113636363636363</v>
       </c>
       <c r="I2">
-        <v>-0.00812489508141682</v>
+        <v>-0.03036221590909091</v>
       </c>
       <c r="J2">
-        <v>-0.00812489508141682</v>
+        <v>-0.03036221590909091</v>
       </c>
       <c r="K2">
-        <v>-22.6</v>
+        <v>-3.43</v>
       </c>
       <c r="L2">
-        <v>-0.03793855967769011</v>
+        <v>-0.006090198863636364</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.746</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.001289319045973038</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.2174927113702624</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.746</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.001289319045973038</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.2174927113702624</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>93</v>
+        <v>62.7</v>
       </c>
       <c r="V2">
-        <v>0.0986423419601188</v>
+        <v>0.1083650190114068</v>
       </c>
       <c r="W2">
-        <v>-0.07053682896379526</v>
+        <v>-0.009198176454813623</v>
       </c>
       <c r="X2">
-        <v>0.05563020963546193</v>
+        <v>0.09300098052294882</v>
       </c>
       <c r="Y2">
-        <v>-0.1261670385992572</v>
+        <v>-0.1021991569777624</v>
       </c>
       <c r="Z2">
-        <v>1.374480849100139</v>
+        <v>1.057851239669422</v>
       </c>
       <c r="AA2">
-        <v>-0.01116751269035533</v>
+        <v>-0.03211870773854245</v>
       </c>
       <c r="AB2">
-        <v>0.0483816825680982</v>
+        <v>0.07467647590376955</v>
       </c>
       <c r="AC2">
-        <v>-0.05954919525845353</v>
+        <v>-0.106795183642312</v>
       </c>
       <c r="AD2">
-        <v>281.9</v>
+        <v>305.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>281.9</v>
+        <v>305.8</v>
       </c>
       <c r="AG2">
-        <v>188.9</v>
+        <v>243.1</v>
       </c>
       <c r="AH2">
-        <v>0.2301788193026864</v>
+        <v>0.3457711442786069</v>
       </c>
       <c r="AI2">
-        <v>0.3107705875868151</v>
+        <v>0.3643946615824595</v>
       </c>
       <c r="AJ2">
-        <v>0.1669170274807811</v>
+        <v>0.2958500669344043</v>
       </c>
       <c r="AK2">
-        <v>0.2320353764893747</v>
+        <v>0.3130714745653574</v>
       </c>
       <c r="AL2">
-        <v>12.3</v>
+        <v>8.17</v>
       </c>
       <c r="AM2">
-        <v>8.770000000000001</v>
+        <v>4.15</v>
       </c>
       <c r="AN2">
-        <v>15.57458563535911</v>
+        <v>70.13761467889908</v>
       </c>
       <c r="AO2">
-        <v>-0.3934959349593495</v>
+        <v>-2.093023255813954</v>
       </c>
       <c r="AP2">
-        <v>10.43646408839779</v>
+        <v>55.75688073394495</v>
       </c>
       <c r="AQ2">
-        <v>-0.5518814139110604</v>
+        <v>-4.120481927710843</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.105</v>
+        <v>0.15</v>
       </c>
       <c r="G3">
-        <v>0.04968944099378882</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="H3">
-        <v>0.03072016115494376</v>
+        <v>0.05113636363636363</v>
       </c>
       <c r="I3">
-        <v>-0.00812489508141682</v>
+        <v>-0.03036221590909091</v>
       </c>
       <c r="J3">
-        <v>-0.00812489508141682</v>
+        <v>-0.03036221590909091</v>
       </c>
       <c r="K3">
-        <v>-22.6</v>
+        <v>-3.43</v>
       </c>
       <c r="L3">
-        <v>-0.03793855967769011</v>
+        <v>-0.006090198863636364</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.746</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.001289319045973038</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.2174927113702624</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.746</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.001289319045973038</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.2174927113702624</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>93</v>
+        <v>62.7</v>
       </c>
       <c r="V3">
-        <v>0.0986423419601188</v>
+        <v>0.1083650190114068</v>
       </c>
       <c r="W3">
-        <v>-0.07053682896379526</v>
+        <v>-0.009198176454813623</v>
       </c>
       <c r="X3">
-        <v>0.05563020963546193</v>
+        <v>0.09300098052294882</v>
       </c>
       <c r="Y3">
-        <v>-0.1261670385992572</v>
+        <v>-0.1021991569777624</v>
       </c>
       <c r="Z3">
-        <v>1.374480849100139</v>
+        <v>1.057851239669422</v>
       </c>
       <c r="AA3">
-        <v>-0.01116751269035533</v>
+        <v>-0.03211870773854245</v>
       </c>
       <c r="AB3">
-        <v>0.0483816825680982</v>
+        <v>0.07467647590376955</v>
       </c>
       <c r="AC3">
-        <v>-0.05954919525845353</v>
+        <v>-0.106795183642312</v>
       </c>
       <c r="AD3">
-        <v>281.9</v>
+        <v>305.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>281.9</v>
+        <v>305.8</v>
       </c>
       <c r="AG3">
-        <v>188.9</v>
+        <v>243.1</v>
       </c>
       <c r="AH3">
-        <v>0.2301788193026864</v>
+        <v>0.3457711442786069</v>
       </c>
       <c r="AI3">
-        <v>0.3107705875868151</v>
+        <v>0.3643946615824595</v>
       </c>
       <c r="AJ3">
-        <v>0.1669170274807811</v>
+        <v>0.2958500669344043</v>
       </c>
       <c r="AK3">
-        <v>0.2320353764893747</v>
+        <v>0.3130714745653574</v>
       </c>
       <c r="AL3">
-        <v>12.3</v>
+        <v>8.17</v>
       </c>
       <c r="AM3">
-        <v>8.770000000000001</v>
+        <v>4.15</v>
       </c>
       <c r="AN3">
-        <v>15.57458563535911</v>
+        <v>70.13761467889908</v>
       </c>
       <c r="AO3">
-        <v>-0.3934959349593495</v>
+        <v>-2.093023255813954</v>
       </c>
       <c r="AP3">
-        <v>10.43646408839779</v>
+        <v>55.75688073394495</v>
       </c>
       <c r="AQ3">
-        <v>-0.5518814139110604</v>
+        <v>-4.120481927710843</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_hospitals_healthcare_facilities.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.15</v>
+        <v>0.134</v>
       </c>
       <c r="G2">
-        <v>0.06818181818181818</v>
+        <v>-0.008713040994143696</v>
       </c>
       <c r="H2">
-        <v>0.05113636363636363</v>
+        <v>-0.02399657191829739</v>
       </c>
       <c r="I2">
-        <v>-0.03036221590909091</v>
+        <v>-0.01971146979003</v>
       </c>
       <c r="J2">
-        <v>-0.03036221590909091</v>
+        <v>-0.01971146979003</v>
       </c>
       <c r="K2">
-        <v>-3.43</v>
+        <v>-23.7</v>
       </c>
       <c r="L2">
-        <v>-0.006090198863636364</v>
+        <v>-0.03385230681331238</v>
       </c>
       <c r="M2">
-        <v>0.746</v>
+        <v>4.07</v>
       </c>
       <c r="N2">
-        <v>0.001289319045973038</v>
+        <v>0.004748016798880075</v>
       </c>
       <c r="O2">
-        <v>-0.2174927113702624</v>
+        <v>-0.1717299578059072</v>
       </c>
       <c r="P2">
-        <v>0.746</v>
+        <v>2.43</v>
       </c>
       <c r="Q2">
-        <v>0.001289319045973038</v>
+        <v>0.00283481101259916</v>
       </c>
       <c r="R2">
-        <v>-0.2174927113702624</v>
+        <v>-0.1025316455696203</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.402948402948403</v>
       </c>
       <c r="U2">
-        <v>62.7</v>
+        <v>61.5</v>
       </c>
       <c r="V2">
-        <v>0.1083650190114068</v>
+        <v>0.07174521698553429</v>
       </c>
       <c r="W2">
-        <v>-0.009198176454813623</v>
+        <v>-0.09367588932806324</v>
       </c>
       <c r="X2">
-        <v>0.09300098052294882</v>
+        <v>0.07832332199540748</v>
       </c>
       <c r="Y2">
-        <v>-0.1021991569777624</v>
+        <v>-0.1719992113234707</v>
       </c>
       <c r="Z2">
-        <v>1.057851239669422</v>
+        <v>1.548893805309735</v>
       </c>
       <c r="AA2">
-        <v>-0.03211870773854245</v>
+        <v>-0.03053097345132744</v>
       </c>
       <c r="AB2">
-        <v>0.07467647590376955</v>
+        <v>0.06763824127735166</v>
       </c>
       <c r="AC2">
-        <v>-0.106795183642312</v>
+        <v>-0.09816921472867909</v>
       </c>
       <c r="AD2">
-        <v>305.8</v>
+        <v>359.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>305.8</v>
+        <v>359.7</v>
       </c>
       <c r="AG2">
-        <v>243.1</v>
+        <v>298.2</v>
       </c>
       <c r="AH2">
-        <v>0.3457711442786069</v>
+        <v>0.2955871476703097</v>
       </c>
       <c r="AI2">
-        <v>0.3643946615824595</v>
+        <v>0.4120274914089347</v>
       </c>
       <c r="AJ2">
-        <v>0.2958500669344043</v>
+        <v>0.2580924355201661</v>
       </c>
       <c r="AK2">
-        <v>0.3130714745653574</v>
+        <v>0.3674676524953789</v>
       </c>
       <c r="AL2">
-        <v>8.17</v>
+        <v>24.8</v>
       </c>
       <c r="AM2">
-        <v>4.15</v>
+        <v>15.92</v>
       </c>
       <c r="AN2">
-        <v>70.13761467889908</v>
+        <v>25.51063829787234</v>
       </c>
       <c r="AO2">
-        <v>-2.093023255813954</v>
+        <v>-0.5564516129032259</v>
       </c>
       <c r="AP2">
-        <v>55.75688073394495</v>
+        <v>21.14893617021277</v>
       </c>
       <c r="AQ2">
-        <v>-4.120481927710843</v>
+        <v>-0.8668341708542714</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.15</v>
+        <v>0.134</v>
       </c>
       <c r="G3">
-        <v>0.06818181818181818</v>
+        <v>-0.008713040994143696</v>
       </c>
       <c r="H3">
-        <v>0.05113636363636363</v>
+        <v>-0.02399657191829739</v>
       </c>
       <c r="I3">
-        <v>-0.03036221590909091</v>
+        <v>-0.01971146979003</v>
       </c>
       <c r="J3">
-        <v>-0.03036221590909091</v>
+        <v>-0.01971146979003</v>
       </c>
       <c r="K3">
-        <v>-3.43</v>
+        <v>-23.7</v>
       </c>
       <c r="L3">
-        <v>-0.006090198863636364</v>
+        <v>-0.03385230681331238</v>
       </c>
       <c r="M3">
-        <v>0.746</v>
+        <v>4.07</v>
       </c>
       <c r="N3">
-        <v>0.001289319045973038</v>
+        <v>0.004748016798880075</v>
       </c>
       <c r="O3">
-        <v>-0.2174927113702624</v>
+        <v>-0.1717299578059072</v>
       </c>
       <c r="P3">
-        <v>0.746</v>
+        <v>2.43</v>
       </c>
       <c r="Q3">
-        <v>0.001289319045973038</v>
+        <v>0.00283481101259916</v>
       </c>
       <c r="R3">
-        <v>-0.2174927113702624</v>
+        <v>-0.1025316455696203</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.402948402948403</v>
       </c>
       <c r="U3">
-        <v>62.7</v>
+        <v>61.5</v>
       </c>
       <c r="V3">
-        <v>0.1083650190114068</v>
+        <v>0.07174521698553429</v>
       </c>
       <c r="W3">
-        <v>-0.009198176454813623</v>
+        <v>-0.09367588932806324</v>
       </c>
       <c r="X3">
-        <v>0.09300098052294882</v>
+        <v>0.07832332199540748</v>
       </c>
       <c r="Y3">
-        <v>-0.1021991569777624</v>
+        <v>-0.1719992113234707</v>
       </c>
       <c r="Z3">
-        <v>1.057851239669422</v>
+        <v>1.548893805309735</v>
       </c>
       <c r="AA3">
-        <v>-0.03211870773854245</v>
+        <v>-0.03053097345132744</v>
       </c>
       <c r="AB3">
-        <v>0.07467647590376955</v>
+        <v>0.06763824127735166</v>
       </c>
       <c r="AC3">
-        <v>-0.106795183642312</v>
+        <v>-0.09816921472867909</v>
       </c>
       <c r="AD3">
-        <v>305.8</v>
+        <v>359.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>305.8</v>
+        <v>359.7</v>
       </c>
       <c r="AG3">
-        <v>243.1</v>
+        <v>298.2</v>
       </c>
       <c r="AH3">
-        <v>0.3457711442786069</v>
+        <v>0.2955871476703097</v>
       </c>
       <c r="AI3">
-        <v>0.3643946615824595</v>
+        <v>0.4120274914089347</v>
       </c>
       <c r="AJ3">
-        <v>0.2958500669344043</v>
+        <v>0.2580924355201661</v>
       </c>
       <c r="AK3">
-        <v>0.3130714745653574</v>
+        <v>0.3674676524953789</v>
       </c>
       <c r="AL3">
-        <v>8.17</v>
+        <v>24.8</v>
       </c>
       <c r="AM3">
-        <v>4.15</v>
+        <v>15.92</v>
       </c>
       <c r="AN3">
-        <v>70.13761467889908</v>
+        <v>25.51063829787234</v>
       </c>
       <c r="AO3">
-        <v>-2.093023255813954</v>
+        <v>-0.5564516129032259</v>
       </c>
       <c r="AP3">
-        <v>55.75688073394495</v>
+        <v>21.14893617021277</v>
       </c>
       <c r="AQ3">
-        <v>-4.120481927710843</v>
+        <v>-0.8668341708542714</v>
       </c>
     </row>
   </sheetData>
